--- a/marketing/paycheck-budget-promo/PaycheckBudget_Light_DEMO.xlsx
+++ b/marketing/paycheck-budget-promo/PaycheckBudget_Light_DEMO.xlsx
@@ -16,16 +16,7 @@
     <sheet name="Savings" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Debt" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Start Here'!$A$1:$H$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Setup'!$A$1:$K$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Dashboard'!$A$1:$O$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Paycheck Budget'!$A$1:$G$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Transactions'!$A$1:$G$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Bill Calendar'!$A$1:$F$18</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Savings'!$A$1:$E$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Debt'!$A$1:$F$13</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -1180,7 +1171,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:Z69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -4104,8 +4095,8 @@
     <mergeCell ref="C15:H15"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.15" right="0.15" top="0.15" bottom="0.15" header="0" footer="0"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -4113,7 +4104,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:Z63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -7102,8 +7093,8 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.15" right="0.15" top="0.15" bottom="0.15" header="0" footer="0"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -7111,7 +7102,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:Z63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -10046,8 +10037,8 @@
     <mergeCell ref="F7:G7"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.15" right="0.15" top="0.15" bottom="0.15" header="0" footer="0"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -10056,7 +10047,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:Z33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -12371,8 +12362,8 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.15" right="0.15" top="0.15" bottom="0.15" header="0" footer="0"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -12380,7 +12371,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:Z504"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -22668,8 +22659,8 @@
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.15" right="0.15" top="0.15" bottom="0.15" header="0" footer="0"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -22677,7 +22668,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:Z63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -25665,8 +25656,8 @@
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.15" right="0.15" top="0.15" bottom="0.15" header="0" footer="0"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -25674,7 +25665,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:Z63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -28495,8 +28486,8 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.15" right="0.15" top="0.15" bottom="0.15" header="0" footer="0"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -28504,7 +28495,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:Z63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -31331,7 +31322,7 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.15" right="0.15" top="0.15" bottom="0.15" header="0" footer="0"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>